--- a/etf_holdings/2026-10-19_common_daily_changes_summary.xlsx
+++ b/etf_holdings/2026-10-19_common_daily_changes_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -469,7 +469,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00991A(新納入)、00980A(新納入)、00403A(新納入)、00985A(新納入)、00405A(新納入)、00407A(新納入)、00993A(新納入)</t>
+          <t>00981A(新納入)、00991A(新納入)、00980A(新納入)、00403A(新納入)、00985A(新納入)、00405A(新納入)、00407A(新納入)、00993A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -499,7 +499,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00991A(新納入)、00982A(新納入)、00403A(新納入)、00985A(新納入)、00992A(新納入)、00405A(新納入)、00993A(新納入)</t>
+          <t>00981A(新納入)、00991A(新納入)、00982A(新納入)、00403A(新納入)、00985A(新納入)、00992A(新納入)、00405A(新納入)、00993A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -511,12 +511,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -529,7 +529,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00980A(新納入)、00982A(新納入)、00403A(新納入)、00985A(新納入)、00405A(新納入)、00407A(新納入)、00993A(新納入)</t>
+          <t>00991A(新納入)、00980A(新納入)、00982A(新納入)、00403A(新納入)、00985A(新納入)、00405A(新納入)、00407A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -541,16 +541,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -559,7 +559,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00980A(新納入)、00982A(新納入)、00403A(新納入)、00985A(新納入)、00405A(新納入)、00407A(新納入)</t>
+          <t>00981A(新納入)、00991A(新納入)、00980A(新納入)、00982A(新納入)、00403A(新納入)、00992A(新納入)、00407A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -571,16 +571,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00991A(新納入)、00980A(新納入)、00403A(新納入)、00992A(新納入)、00407A(新納入)、00993A(新納入)</t>
+          <t>00981A(新納入)、00991A(新納入)、00980A(新納入)、00403A(新納入)、00985A(新納入)、00992A(新納入)、00405A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -601,16 +601,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00991A(新納入)、00980A(新納入)、00982A(新納入)、00403A(新納入)、00992A(新納入)、00407A(新納入)</t>
+          <t>00981A(新納入)、00980A(新納入)、00982A(新納入)、00403A(新納入)、00985A(新納入)、00405A(新納入)、00407A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -631,12 +631,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -649,7 +649,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00991A(新納入)、00980A(新納入)、00403A(新納入)、00985A(新納入)、00992A(新納入)、00405A(新納入)</t>
+          <t>00981A(新納入)、00991A(新納入)、00980A(新納入)、00403A(新納入)、00992A(新納入)、00407A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -661,16 +661,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>00981A(199,000)、00403A(新納入)、00985A(新納入)、00992A(新納入)、00407A(新納入)、00993A(新納入)</t>
+          <t>00981A(新納入)、00991A(新納入)、00980A(新納入)、00403A(新納入)、00985A(新納入)、00993A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -709,7 +709,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00991A(新納入)、00980A(新納入)、00403A(新納入)、00985A(新納入)、00993A(新納入)</t>
+          <t>00981A(新納入)、00991A(新納入)、00980A(新納入)、00403A(新納入)、00985A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -721,12 +721,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -739,7 +739,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00980A(新納入)、00982A(新納入)、00403A(100,000)、00992A(新納入)、00405A(新納入)</t>
+          <t>00981A(199,000)、00403A(新納入)、00985A(新納入)、00992A(新納入)、00407A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -751,16 +751,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -769,7 +769,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>00982A(新納入)、00403A(新納入)、00992A(新納入)、00407A(新納入)、00993A(新納入)</t>
+          <t>00991A(新納入)、00980A(新納入)、00982A(新納入)、00992A(新納入)、00407A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -781,16 +781,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00991A(新納入)、00980A(新納入)、00403A(新納入)、00985A(新納入)</t>
+          <t>00981A(新納入)、00992A(新納入)、00405A(新納入)、00407A(新納入)、00993A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -811,16 +811,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>00980A(新納入)、00403A(新納入)、00985A(新納入)、00407A(新納入)、00993A(新納入)</t>
+          <t>00991A(新納入)、00980A(新納入)、00982A(新納入)、00403A(100,000)、00992A(新納入)、00405A(新納入)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -841,12 +841,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -859,7 +859,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00980A(新納入)、00982A(新納入)、00992A(新納入)、00407A(新納入)</t>
+          <t>00982A(新納入)、00403A(新納入)、00992A(新納入)、00407A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -871,12 +871,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -889,7 +889,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00980A(新納入)、00403A(新納入)、00405A(新納入)、00993A(新納入)</t>
+          <t>00981A(新納入)、00991A(新納入)、00403A(新納入)、00993A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -901,12 +901,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00991A(新納入)、00992A(新納入)、00405A(新納入)、00993A(新納入)</t>
+          <t>00980A(新納入)、00403A(新納入)、00985A(新納入)、00407A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -931,12 +931,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00992A(新納入)、00405A(新納入)、00407A(新納入)、00993A(新納入)</t>
+          <t>00991A(新納入)、00980A(新納入)、00407A(新納入)、00993A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -961,12 +961,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00980A(新納入)、00403A(新納入)、00407A(新納入)、00993A(新納入)</t>
+          <t>00981A(新納入)、00991A(新納入)、00403A(新納入)、00405A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -991,16 +991,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>00403A(新納入)、00405A(新納入)、00407A(新納入)、00993A(新納入)</t>
+          <t>00981A(新納入)、00980A(新納入)、00403A(新納入)、00405A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1021,16 +1021,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>00981A(75,000)、00991A(新納入)、00992A(新納入)、00405A(新納入)</t>
+          <t>00981A(新納入)、00991A(新納入)、00992A(新納入)、00405A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1051,16 +1051,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00991A(新納入)、00403A(新納入)、00993A(新納入)</t>
+          <t>00981A(新納入)、00980A(新納入)、00403A(新納入)、00407A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1081,12 +1081,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00980A(新納入)、00407A(新納入)、00993A(新納入)</t>
+          <t>00403A(新納入)、00405A(新納入)、00407A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1111,12 +1111,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>00980A(新納入)、00982A(新納入)、00985A(334,000)、00992A(新納入)</t>
+          <t>00981A(75,000)、00991A(新納入)、00992A(新納入)、00405A(新納入)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1141,12 +1141,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1154,29 +1154,29 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>00982A(新納入)、00985A(新納入)、00405A(新納入)、00993A(新納入)</t>
+          <t>00980A(新納入)、00985A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00991A(-400,000)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00991A(新納入)、00403A(新納入)、00405A(新納入)</t>
+          <t>00980A(新納入)、00982A(新納入)、00985A(334,000)、00992A(新納入)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1201,12 +1201,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1214,29 +1214,29 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>00985A(新納入)、00992A(新納入)、00993A(新納入)</t>
+          <t>00982A(新納入)、00985A(新納入)、00405A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>00403A(-200,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1244,29 +1244,29 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>全部加碼</t>
+          <t>混合</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>00980A(新納入)、00985A(新納入)、00992A(新納入)、00405A(新納入)</t>
+          <t>00985A(新納入)、00992A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>00403A(-200,000)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>00985A(新納入)、00405A(新納入)、00407A(新納入)、00993A(新納入)</t>
+          <t>00991A(新納入)、00982A(新納入)、00985A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1291,12 +1291,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>00982A(新納入)、00985A(新納入)、00405A(新納入)、00407A(新納入)</t>
+          <t>00992A(新納入)、00407A(新納入)、00993A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1321,12 +1321,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00980A(新納入)、00992A(新納入)、00405A(新納入)</t>
+          <t>00980A(新納入)、00985A(新納入)、00992A(新納入)、00405A(新納入)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1351,12 +1351,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00980A(新納入)、00403A(新納入)、00407A(新納入)</t>
+          <t>00981A(新納入)、00982A(新納入)、00403A(25,000)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1381,16 +1381,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>昇達科</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>00403A(新納入)、00407A(新納入)、00993A(新納入)</t>
+          <t>00985A(新納入)、00405A(新納入)、00407A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1411,16 +1411,16 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00405A(新納入)、00407A(新納入)</t>
+          <t>00980A(新納入)、00982A(新納入)、00407A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1441,46 +1441,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>混合</t>
+          <t>全部加碼</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>00980A(新納入)、00985A(新納入)</t>
+          <t>00981A(新納入)、00985A(新納入)、00405A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>00991A(-400,000)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00991A(新納入)、00980A(新納入)</t>
+          <t>00981A(新納入)、00992A(新納入)、00407A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1501,16 +1501,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>00403A(新納入)、00992A(新納入)、00993A(新納入)</t>
+          <t>00982A(新納入)、00985A(新納入)、00405A(新納入)、00407A(新納入)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1531,16 +1531,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00403A(新納入)、00407A(新納入)</t>
+          <t>00981A(新納入)、00980A(新納入)、00992A(新納入)、00405A(新納入)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1561,16 +1561,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>00982A(新納入)、00403A(新納入)、00993A(新納入)</t>
+          <t>00991A(新納入)、00980A(新納入)、00403A(新納入)、00407A(新納入)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1591,12 +1591,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00403A(新納入)、00993A(新納入)</t>
+          <t>00403A(新納入)、00407A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1621,12 +1621,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00982A(新納入)、00985A(新納入)</t>
+          <t>00981A(新納入)、00405A(新納入)、00407A(新納入)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1651,12 +1651,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>00991A(200,000)、00980A(新納入)、00992A(新納入)</t>
+          <t>00981A(新納入)、00991A(新納入)、00980A(新納入)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1681,12 +1681,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00980A(新納入)、00993A(新納入)</t>
+          <t>00403A(新納入)、00992A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1711,12 +1711,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>00992A(新納入)、00407A(新納入)、00993A(新納入)</t>
+          <t>00981A(新納入)、00403A(新納入)、00407A(新納入)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1741,12 +1741,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00982A(新納入)、00403A(25,000)</t>
+          <t>00982A(新納入)、00403A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1771,12 +1771,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>00980A(新納入)、00982A(新納入)、00407A(新納入)</t>
+          <t>00981A(新納入)、00403A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -1801,12 +1801,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00985A(新納入)、00405A(新納入)</t>
+          <t>00991A(新納入)、00985A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>中信金</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00992A(新納入)、00407A(新納入)</t>
+          <t>00991A(新納入)、00980A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1861,12 +1861,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>00980A(新納入)、00982A(新納入)、00992A(新納入)</t>
+          <t>00991A(200,000)、00980A(新納入)、00992A(新納入)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -1891,12 +1891,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>00980A(新納入)、00403A(新納入)、00985A(新納入)</t>
+          <t>00991A(新納入)、00980A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -1921,12 +1921,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00403A(新納入)、00985A(新納入)</t>
+          <t>00991A(新納入)、00980A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -1951,12 +1951,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00405A(新納入)、00407A(新納入)</t>
+          <t>00980A(新納入)、00407A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -1981,12 +1981,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>00982A(9,000)、00985A(新納入)、00407A(新納入)</t>
+          <t>00405A(新納入)、00407A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2011,12 +2011,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00992A(新納入)、00405A(新納入)</t>
+          <t>00980A(新納入)、00982A(新納入)、00992A(新納入)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2041,12 +2041,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00982A(新納入)、00403A(新納入)</t>
+          <t>00981A(新納入)、00993A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2071,16 +2071,16 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>00405A(新納入)、00407A(新納入)</t>
+          <t>00981A(新納入)、00405A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2101,16 +2101,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>00985A(新納入)、00993A(新納入)</t>
+          <t>00980A(新納入)、00403A(新納入)、00985A(新納入)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2131,16 +2131,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>00981A(204,000)、00405A(新納入)</t>
+          <t>00981A(新納入)、00403A(新納入)、00985A(新納入)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2161,16 +2161,16 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00992A(新納入)</t>
+          <t>00981A(新納入)、00405A(新納入)、00407A(新納入)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2191,16 +2191,16 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>00982A(新納入)、00985A(新納入)</t>
+          <t>00982A(9,000)、00985A(新納入)、00407A(新納入)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2221,16 +2221,16 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00407A(新納入)</t>
+          <t>00981A(新納入)、00992A(新納入)、00405A(新納入)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2251,16 +2251,16 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00985A(新納入)</t>
+          <t>00981A(新納入)、00982A(新納入)、00403A(新納入)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2281,12 +2281,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>00982A(新納入)、00993A(新納入)</t>
+          <t>00405A(新納入)、00407A(新納入)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2311,12 +2311,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00985A(新納入)</t>
+          <t>00985A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2341,12 +2341,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00403A(新納入)</t>
+          <t>00981A(204,000)、00405A(新納入)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2371,12 +2371,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00980A(新納入)</t>
+          <t>00991A(新納入)、00992A(新納入)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2401,12 +2401,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00982A(新納入)</t>
+          <t>00982A(新納入)、00985A(新納入)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2431,12 +2431,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00982A(新納入)</t>
+          <t>00991A(新納入)、00407A(新納入)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2461,12 +2461,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>中信金</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00980A(新納入)</t>
+          <t>00991A(新納入)、00985A(新納入)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2491,12 +2491,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>00991A(100,000)、00985A(新納入)</t>
+          <t>00982A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2521,12 +2521,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2637</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>慧洋-KY</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00980A(新納入)</t>
+          <t>00981A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2551,12 +2551,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>00985A(新納入)、00993A(新納入)</t>
+          <t>00991A(新納入)、00403A(新納入)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2581,12 +2581,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>弘塑</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>00992A(新納入)、00407A(新納入)</t>
+          <t>00991A(新納入)、00980A(新納入)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2611,12 +2611,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>00980A(新納入)、00407A(新納入)</t>
+          <t>00991A(新納入)、00982A(新納入)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2641,12 +2641,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>00403A(新納入)、00405A(新納入)</t>
+          <t>00991A(新納入)、00982A(新納入)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2671,12 +2671,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>00405A(新納入)、00407A(新納入)</t>
+          <t>00991A(100,000)、00985A(新納入)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2701,12 +2701,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>日電貿</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>00982A(新納入)、00403A(新納入)</t>
+          <t>00982A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2731,12 +2731,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>00992A(新納入)、00993A(新納入)</t>
+          <t>00985A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2761,12 +2761,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>宜鼎</t>
+          <t>弘塑</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -2791,12 +2791,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>00982A(新納入)、00403A(新納入)</t>
+          <t>00403A(新納入)、00405A(新納入)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2821,12 +2821,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>00991A(新納入)、00980A(新納入)</t>
+          <t>00982A(新納入)、00403A(新納入)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -2851,12 +2851,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>00982A(新納入)、00403A(新納入)</t>
+          <t>00992A(新納入)、00993A(新納入)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -2881,12 +2881,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>宜鼎</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00993A(新納入)</t>
+          <t>00992A(新納入)、00407A(新納入)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -2911,12 +2911,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>00981A(新納入)、00405A(新納入)</t>
+          <t>00407A(新納入)、00400A(新納入)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -2941,12 +2941,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>00403A(新納入)、00405A(新納入)</t>
+          <t>00982A(新納入)、00403A(新納入)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -2971,12 +2971,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>00985A(新納入)、00405A(新納入)</t>
+          <t>00991A(新納入)、00980A(新納入)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3001,12 +3001,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>00405A(新納入)、00993A(新納入)</t>
+          <t>00982A(新納入)、00403A(新納入)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3031,12 +3031,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>00980A(新納入)、00985A(新納入)</t>
+          <t>00403A(新納入)、00405A(新納入)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3061,12 +3061,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -3079,10 +3079,160 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>00985A(新納入)、00405A(新納入)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>7750</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>新代</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>00985A(新納入)、00400A(新納入)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>00991A(新納入)、00400A(新納入)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>8021</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>尖點</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>2</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>00405A(新納入)、00993A(新納入)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>00980A(新納入)、00985A(新納入)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>2</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>全部加碼</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>00981A(新納入)、00980A(新納入)</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
